--- a/simulations/AO_real/economics_AO_real.xlsx
+++ b/simulations/AO_real/economics_AO_real.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AO_real\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09EE40C6-2CC1-454D-A89A-537B3C151F75}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B26BAAC-5624-4777-B3AC-640F47563C7B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17265" windowHeight="5775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAPEX" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="153">
   <si>
     <t>Cost factors</t>
   </si>
@@ -637,14 +637,45 @@
   <si>
     <t>CEPCI 2015</t>
   </si>
+  <si>
+    <t>Parkinson</t>
+  </si>
+  <si>
+    <t>Nabera</t>
+  </si>
+  <si>
+    <t>World bank</t>
+  </si>
+  <si>
+    <t>Iasonas</t>
+  </si>
+  <si>
+    <t>Merck? - need to check</t>
+  </si>
+  <si>
+    <t>Current wind hydrogen price</t>
+  </si>
+  <si>
+    <t>$ per ton</t>
+  </si>
+  <si>
+    <t>Future fossil hydrogen price</t>
+  </si>
+  <si>
+    <t>Future wind hydrogen price</t>
+  </si>
+  <si>
+    <t>Current fossil hydrogen price</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -796,7 +827,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -912,6 +943,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -933,6 +965,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1406,16 +1439,16 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="53"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="54"/>
       <c r="L13" s="33" t="s">
         <v>89</v>
       </c>
@@ -1619,16 +1652,16 @@
       <c r="T16" s="47"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
-      <c r="G17" s="52"/>
-      <c r="H17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="54"/>
       <c r="L17" s="33" t="s">
         <v>137</v>
       </c>
@@ -1744,16 +1777,16 @@
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A21" s="51" t="s">
+      <c r="A21" s="52" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="53"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="54"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -2130,16 +2163,16 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="56"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -2198,16 +2231,16 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="51" t="s">
+      <c r="A36" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="53"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="54"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
@@ -2266,16 +2299,16 @@
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="51" t="s">
+      <c r="A39" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="53"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="54"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
@@ -2569,11 +2602,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="57">
+      <c r="A3" s="58">
         <v>2022</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
@@ -2587,11 +2620,11 @@
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
@@ -2630,19 +2663,19 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
-      <c r="B9" s="53"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="17">
         <f>SUM(C6:C8)</f>
         <v>7.3406250000000002</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
@@ -2657,19 +2690,19 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="29">
         <f>C11</f>
         <v>1.2302313863938941</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="53"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="54"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -2696,19 +2729,19 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="29">
         <f>SUM(C14:C15)</f>
         <v>6.6372571860307392</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="51" t="s">
+      <c r="A17" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="54"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
@@ -2723,18 +2756,18 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="57"/>
-      <c r="B19" s="57"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="17">
         <f>C18</f>
         <v>0.67170633697106619</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="53"/>
+      <c r="B20" s="54"/>
       <c r="C20" s="17">
         <f>C9+C12+C16+C19</f>
         <v>15.8798199093957</v>
@@ -2760,22 +2793,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:G20"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="11"/>
     <col min="2" max="2" width="21.42578125" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.140625" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.85546875" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>23</v>
       </c>
@@ -2792,16 +2825,16 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
         <v>99</v>
       </c>
@@ -2819,7 +2852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>139</v>
       </c>
@@ -2831,7 +2864,6 @@
         <v>2.46937499350752</v>
       </c>
       <c r="E6" s="42">
-        <f>1260*C20/C17</f>
         <v>1846.5517241379312</v>
       </c>
       <c r="F6" s="42">
@@ -2842,8 +2874,11 @@
         <f>F6/Summary!$C$23</f>
         <v>0.12159689975531821</v>
       </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="41" t="s">
         <v>138</v>
       </c>
@@ -2855,18 +2890,21 @@
         <v>2.46937499350752</v>
       </c>
       <c r="E7" s="42">
-        <v>5236.1000000000004</v>
+        <v>6210</v>
       </c>
       <c r="F7" s="42">
         <f>D7*E7</f>
-        <v>12929.894403504726</v>
+        <v>15334.818709681698</v>
       </c>
       <c r="G7" s="11">
         <f>F7/Summary!$C$23</f>
-        <v>0.34480134971906312</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+        <v>0.40893343934519616</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="41" t="s">
         <v>140</v>
       </c>
@@ -2888,17 +2926,20 @@
         <f>F8/Summary!$C$23</f>
         <v>1.7534231211380544</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="51" t="s">
+      <c r="H8" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>24</v>
       </c>
@@ -2922,7 +2963,7 @@
         <v>1.4292666501166196E-3</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
         <v>141</v>
       </c>
@@ -2945,8 +2986,11 @@
         <f>F11/Summary!$C$23</f>
         <v>1.4012332202271671E-2</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>25</v>
       </c>
@@ -2968,8 +3012,11 @@
         <f>F12/Summary!$C$23</f>
         <v>8.2752625114666644E-3</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>104</v>
       </c>
@@ -2983,7 +3030,7 @@
         <v>569.61418295210137</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>105</v>
       </c>
@@ -2994,26 +3041,28 @@
       <c r="E14" s="19"/>
       <c r="F14" s="19">
         <f>(F5+F7+F8+F10+F11+F12)/1000000*8000</f>
-        <v>636.57470896570408</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+        <v>655.8141034151198</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="15"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>151</v>
+      </c>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>142</v>
       </c>
@@ -3021,31 +3070,76 @@
         <v>556.79999999999995</v>
       </c>
       <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="15">
+        <v>3500</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>84</v>
       </c>
       <c r="C18" s="23">
         <v>603.1</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E18" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="21">
         <v>607.5</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E19" s="11">
+        <v>6210</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
         <v>91</v>
       </c>
       <c r="C20" s="21">
         <v>816</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E21" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E22" s="15">
+        <f>AVERAGE(1.2,2.1)*1000</f>
+        <v>1650</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="59">
+        <f>(E22-E24)/E24*100</f>
+        <v>-10.644257703081239</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E23" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E24" s="51">
+        <v>1846.5517241379312</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3070,14 +3164,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="58" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="E2" s="57" t="s">
+      <c r="C2" s="58"/>
+      <c r="E2" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="F2" s="57"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
@@ -3359,7 +3453,7 @@
       </c>
       <c r="F20" s="17">
         <f>OPEX!F14</f>
-        <v>636.57470896570408</v>
+        <v>655.8141034151198</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
@@ -3375,7 +3469,7 @@
       </c>
       <c r="F21" s="17">
         <f>(F18+F19+F20)</f>
-        <v>647.51792211430029</v>
+        <v>666.75731656371602</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
@@ -3391,7 +3485,7 @@
       </c>
       <c r="F22" s="17">
         <f>(F21)*1000000/8000</f>
-        <v>80939.740264287539</v>
+        <v>83344.664570464505</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
@@ -3422,7 +3516,7 @@
       </c>
       <c r="F24" s="44">
         <f>F22/F23</f>
-        <v>2.1584191500799936</v>
+        <v>2.2225512397061267</v>
       </c>
     </row>
   </sheetData>
